--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView windowWidth="21000" windowHeight="14005"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -106,7 +119,24 @@
     <t>true</t>
   </si>
   <si>
-    <t>item.xlsx</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.xlsx</t>
+    </r>
   </si>
   <si>
     <t>booty.TbBooty</t>
@@ -115,42 +145,223 @@
     <t>Booty</t>
   </si>
   <si>
-    <t>booty.xlsx</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>奖励表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.xlsx</t>
+    </r>
   </si>
   <si>
     <t>id,sub_id</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>funcConfig.TbFuncConfig</t>
+  </si>
+  <si>
+    <t>FuncConfig</t>
+  </si>
+  <si>
+    <t>系统功能表.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,11 +370,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFc6efce"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -173,16 +565,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -190,45 +597,315 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -236,10 +913,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -277,71 +954,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -369,7 +1046,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -392,11 +1069,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -405,13 +1082,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -421,7 +1098,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -430,7 +1107,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -439,7 +1116,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -447,10 +1124,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -510,128 +1187,118 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="20.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="32.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.4324324324324" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.4324324324324" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5765765765766" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.4324324324324" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.4324324324324" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.4234234234234" style="1" customWidth="1"/>
+    <col min="7" max="9" width="18.009009009009" style="1" customWidth="1"/>
+    <col min="10" max="11" width="12.4324324324324" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="21.75" customHeight="1" spans="1:11">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="21.75" customHeight="1" spans="1:11">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="21.75" customHeight="1" spans="1:11">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="2"/>
+    <row r="4" ht="17.25" customHeight="1" spans="2:5">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -641,18 +1308,11 @@
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="2"/>
+    <row r="5" ht="17.25" customHeight="1" spans="2:7">
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
@@ -662,21 +1322,32 @@
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="14005"/>
+    <workbookView windowWidth="24500" windowHeight="16860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -899,13 +899,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1196,16 +1189,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="12.4324324324324" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.4324324324324" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5765765765766" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.4324324324324" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.4324324324324" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.4234234234234" style="1" customWidth="1"/>
-    <col min="7" max="9" width="18.009009009009" style="1" customWidth="1"/>
-    <col min="10" max="11" width="12.4324324324324" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.4363636363636" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.4363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.4363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.4272727272727" style="1" customWidth="1"/>
+    <col min="7" max="9" width="18.0090909090909" style="1" customWidth="1"/>
+    <col min="10" max="11" width="12.4363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:11">

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24500" windowHeight="16860"/>
+    <workbookView windowWidth="20150" windowHeight="17080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -126,7 +126,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>道具表</t>
+      <t>道具表@道具表</t>
     </r>
     <r>
       <rPr>
@@ -137,6 +137,9 @@
       </rPr>
       <t>.xlsx</t>
     </r>
+  </si>
+  <si>
+    <t>c,s</t>
   </si>
   <si>
     <t>booty.TbBooty</t>
@@ -178,6 +181,27 @@
   </si>
   <si>
     <t>系统功能表.xlsx</t>
+  </si>
+  <si>
+    <t>item.TbGetWay</t>
+  </si>
+  <si>
+    <t>ItemGetWay</t>
+  </si>
+  <si>
+    <t>获取途径表@道具表.xlsx</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>item.TbCurrencyConfig</t>
+  </si>
+  <si>
+    <t>CurrencyConfig</t>
+  </si>
+  <si>
+    <t>货币表@道具表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1188,16 +1212,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.4363636363636" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.4363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.2727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.0909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="49.4545454545455" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.4363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.4272727272727" style="1" customWidth="1"/>
-    <col min="7" max="9" width="18.0090909090909" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.0090909090909" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.6363636363636" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.0090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="12.4363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1291,7 +1317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1" spans="2:5">
+    <row r="4" ht="17.25" customHeight="1" spans="1:11">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1304,39 +1330,76 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" spans="2:7">
+    <row r="5" ht="17.25" customHeight="1" spans="1:11">
       <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:11">
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20150" windowHeight="17080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -113,7 +113,7 @@
     <t>item.TbItem</t>
   </si>
   <si>
-    <t>Item</t>
+    <t>ItemConfig</t>
   </si>
   <si>
     <t>true</t>
@@ -145,7 +145,7 @@
     <t>booty.TbBooty</t>
   </si>
   <si>
-    <t>Booty</t>
+    <t>BootyConfig</t>
   </si>
   <si>
     <r>
@@ -174,7 +174,7 @@
     <t/>
   </si>
   <si>
-    <t>funcConfig.TbFuncConfig</t>
+    <t>funcConfig.TbFunc</t>
   </si>
   <si>
     <t>FuncConfig</t>
@@ -186,7 +186,7 @@
     <t>item.TbGetWay</t>
   </si>
   <si>
-    <t>ItemGetWay</t>
+    <t>ItemGetWayConfig</t>
   </si>
   <si>
     <t>获取途径表@道具表.xlsx</t>
@@ -195,13 +195,67 @@
     <t>c</t>
   </si>
   <si>
-    <t>item.TbCurrencyConfig</t>
+    <t>item.TbCurrency</t>
   </si>
   <si>
     <t>CurrencyConfig</t>
   </si>
   <si>
     <t>货币表@道具表.xlsx</t>
+  </si>
+  <si>
+    <t>item.TbItemExchange</t>
+  </si>
+  <si>
+    <t>ItemExchangeConfig</t>
+  </si>
+  <si>
+    <t>道具转化表@道具表.xlsx</t>
+  </si>
+  <si>
+    <t>battle.TbTower</t>
+  </si>
+  <si>
+    <t>TowerConfig</t>
+  </si>
+  <si>
+    <t>基础建筑表@局内.xlsx</t>
+  </si>
+  <si>
+    <t>battle.TbBullet</t>
+  </si>
+  <si>
+    <t>BulletConfig</t>
+  </si>
+  <si>
+    <t>子弹表@局内.xlsx</t>
+  </si>
+  <si>
+    <t>battle.TbUnit</t>
+  </si>
+  <si>
+    <t>UnitConfig</t>
+  </si>
+  <si>
+    <t>基础单位表@局内.xlsx</t>
+  </si>
+  <si>
+    <t>battle.TbBuff</t>
+  </si>
+  <si>
+    <t>BuffConfig</t>
+  </si>
+  <si>
+    <t>基础Buff表@Buff.xlsx</t>
+  </si>
+  <si>
+    <t>battle.TbStatus</t>
+  </si>
+  <si>
+    <t>StatuConfig</t>
+  </si>
+  <si>
+    <t>基础状态表@Buff.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1212,16 +1266,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.2727272727273" style="1" customWidth="1"/>
     <col min="3" max="3" width="37.0909090909091" style="1" customWidth="1"/>
-    <col min="4" max="4" width="49.4545454545455" style="1" customWidth="1"/>
+    <col min="4" max="4" width="76.4545454545455" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.4363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.4272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.0090909090909" style="1" customWidth="1"/>
+    <col min="7" max="7" width="40.0909090909091" style="1" customWidth="1"/>
     <col min="8" max="8" width="32.6363636363636" style="1" customWidth="1"/>
     <col min="9" max="9" width="18.0090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="12.4363636363636" style="1" customWidth="1"/>
@@ -1402,6 +1456,90 @@
         <v>46</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -256,6 +256,33 @@
   </si>
   <si>
     <t>基础状态表@Buff.xlsx</t>
+  </si>
+  <si>
+    <t>level.TbLevelBase</t>
+  </si>
+  <si>
+    <t>LevelBaseConfig</t>
+  </si>
+  <si>
+    <t>关卡基础表@关卡.xlsx</t>
+  </si>
+  <si>
+    <t>level.TbWave</t>
+  </si>
+  <si>
+    <t>WaveConfig</t>
+  </si>
+  <si>
+    <t>关卡波次表@关卡.xlsx</t>
+  </si>
+  <si>
+    <t>res.TbModel</t>
+  </si>
+  <si>
+    <t>ModelConfig</t>
+  </si>
+  <si>
+    <t>模型配置.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1293,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" style="1" customWidth="1"/>
@@ -1540,6 +1567,48 @@
         <v>64</v>
       </c>
     </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
